--- a/Result/profitability/3066.xlsx
+++ b/Result/profitability/3066.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.7</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1675</v>
+        <v>0.405</v>
       </c>
       <c r="N2" t="n">
-        <v>27.0375</v>
+        <v>27.3325</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.6</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.28125</v>
+        <v>0.34</v>
       </c>
       <c r="N3" t="n">
-        <v>22.23375</v>
+        <v>24.27625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.53</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3375</v>
+        <v>0.3925</v>
       </c>
       <c r="N4" t="n">
-        <v>18.88125</v>
+        <v>19.09375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.8</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.31875</v>
+        <v>0.4225</v>
       </c>
       <c r="N5" t="n">
-        <v>13.73</v>
+        <v>16.02</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>-0.22</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.21625</v>
+        <v>0.3475</v>
       </c>
       <c r="N6" t="n">
-        <v>13.1275</v>
+        <v>10.05</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.44</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.31875</v>
+        <v>0.265</v>
       </c>
       <c r="N7" t="n">
-        <v>6.5375</v>
+        <v>6.04375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.36</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.39125</v>
+        <v>0.155</v>
       </c>
       <c r="N8" t="n">
-        <v>2.675</v>
+        <v>2.49125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>-0.38</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.50375</v>
+        <v>-0.5037499999999999</v>
       </c>
       <c r="N9" t="n">
         <v>-0.8062500000000001</v>
@@ -1645,7 +1645,7 @@
         <v>-0.1</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.42875</v>
+        <v>-0.4287499999999999</v>
       </c>
       <c r="N10" t="n">
         <v>2.945</v>
@@ -1899,7 +1899,7 @@
         <v>0.31</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.255</v>
+        <v>-0.2549999999999999</v>
       </c>
       <c r="N12" t="n">
         <v>9.955</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3066</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>75</v>
+      </c>
+      <c r="D75" t="n">
+        <v>49</v>
+      </c>
+      <c r="E75" t="n">
+        <v>26</v>
+      </c>
+      <c r="F75" t="n">
+        <v>34.28</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-21</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-28.02%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>460</v>
+      </c>
+      <c r="J75" t="n">
+        <v>439</v>
+      </c>
+      <c r="K75" t="n">
+        <v>406</v>
+      </c>
+      <c r="L75" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>33.195</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>4.369999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>8.403846153846153</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.469999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.04111888111888107</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-5.701923076923077</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>18.32</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.147869674185463</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
